--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524730</v>
+        <v>122524742</v>
       </c>
       <c r="B2" t="n">
         <v>57395</v>
@@ -703,12 +703,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338491</v>
+        <v>338430</v>
       </c>
       <c r="R2" t="n">
-        <v>6421253</v>
+        <v>6421185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524722</v>
+        <v>122524730</v>
       </c>
       <c r="B3" t="n">
         <v>57395</v>
@@ -823,20 +827,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pussen, Vg</t>
+          <t>Baskanäs, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338469</v>
+        <v>338491</v>
       </c>
       <c r="R3" t="n">
-        <v>6421084</v>
+        <v>6421253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524742</v>
+        <v>122524722</v>
       </c>
       <c r="B4" t="n">
         <v>57395</v>
@@ -933,11 +937,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -948,14 +948,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baskanäs, Vg</t>
+          <t>Pussen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338430</v>
+        <v>338469</v>
       </c>
       <c r="R4" t="n">
-        <v>6421185</v>
+        <v>6421084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524742</v>
+        <v>122524722</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -703,11 +708,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -718,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baskanäs, Vg</t>
+          <t>Pussen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338430</v>
+        <v>338469</v>
       </c>
       <c r="R2" t="n">
-        <v>6421185</v>
+        <v>6421084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +798,7 @@
         <v>122524730</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,6 +812,11 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -909,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524722</v>
+        <v>122524742</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,6 +933,11 @@
       <c r="E4" t="n">
         <v>100049</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -937,7 +948,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -948,14 +963,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pussen, Vg</t>
+          <t>Baskanäs, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338469</v>
+        <v>338430</v>
       </c>
       <c r="R4" t="n">
-        <v>6421084</v>
+        <v>6421185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524722</v>
+        <v>122524742</v>
       </c>
       <c r="B2" t="n">
         <v>57399</v>
@@ -708,7 +708,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -719,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pussen, Vg</t>
+          <t>Baskanäs, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338469</v>
+        <v>338430</v>
       </c>
       <c r="R2" t="n">
-        <v>6421084</v>
+        <v>6421185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524730</v>
+        <v>122524722</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -833,20 +837,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baskanäs, Vg</t>
+          <t>Pussen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338491</v>
+        <v>338469</v>
       </c>
       <c r="R3" t="n">
-        <v>6421253</v>
+        <v>6421084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524742</v>
+        <v>122524730</v>
       </c>
       <c r="B4" t="n">
         <v>57399</v>
@@ -948,16 +952,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338430</v>
+        <v>338491</v>
       </c>
       <c r="R4" t="n">
-        <v>6421185</v>
+        <v>6421253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524742</v>
+        <v>122524722</v>
       </c>
       <c r="B2" t="n">
         <v>57399</v>
@@ -708,11 +708,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -723,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baskanäs, Vg</t>
+          <t>Pussen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338430</v>
+        <v>338469</v>
       </c>
       <c r="R2" t="n">
-        <v>6421185</v>
+        <v>6421084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524722</v>
+        <v>122524742</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -832,7 +828,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -843,14 +843,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pussen, Vg</t>
+          <t>Baskanäs, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338469</v>
+        <v>338430</v>
       </c>
       <c r="R3" t="n">
-        <v>6421084</v>
+        <v>6421185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524722</v>
+        <v>122524742</v>
       </c>
       <c r="B2" t="n">
         <v>57399</v>
@@ -708,7 +708,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -719,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pussen, Vg</t>
+          <t>Baskanäs, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338469</v>
+        <v>338430</v>
       </c>
       <c r="R2" t="n">
-        <v>6421084</v>
+        <v>6421185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524742</v>
+        <v>122524730</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -828,16 +832,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338430</v>
+        <v>338491</v>
       </c>
       <c r="R3" t="n">
-        <v>6421185</v>
+        <v>6421253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524730</v>
+        <v>122524722</v>
       </c>
       <c r="B4" t="n">
         <v>57399</v>
@@ -957,20 +957,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baskanäs, Vg</t>
+          <t>Pussen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338491</v>
+        <v>338469</v>
       </c>
       <c r="R4" t="n">
-        <v>6421253</v>
+        <v>6421084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524742</v>
+        <v>122524722</v>
       </c>
       <c r="B2" t="n">
         <v>57494</v>
@@ -708,11 +708,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -723,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baskanäs, Vg</t>
+          <t>Pussen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338430</v>
+        <v>338469</v>
       </c>
       <c r="R2" t="n">
-        <v>6421185</v>
+        <v>6421084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524722</v>
+        <v>122524730</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -837,20 +833,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pussen, Vg</t>
+          <t>Baskanäs, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338469</v>
+        <v>338491</v>
       </c>
       <c r="R3" t="n">
-        <v>6421084</v>
+        <v>6421253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524730</v>
+        <v>122524742</v>
       </c>
       <c r="B4" t="n">
         <v>57494</v>
@@ -952,12 +948,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338491</v>
+        <v>338430</v>
       </c>
       <c r="R4" t="n">
-        <v>6421253</v>
+        <v>6421185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524730</v>
+        <v>122524742</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -828,12 +828,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338491</v>
+        <v>338430</v>
       </c>
       <c r="R3" t="n">
-        <v>6421253</v>
+        <v>6421185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524742</v>
+        <v>122524730</v>
       </c>
       <c r="B4" t="n">
         <v>57494</v>
@@ -948,16 +952,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338430</v>
+        <v>338491</v>
       </c>
       <c r="R4" t="n">
-        <v>6421185</v>
+        <v>6421253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5040-2025 artfynd.xlsx
+++ b/artfynd/A 5040-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524722</v>
+        <v>122524742</v>
       </c>
       <c r="B2" t="n">
         <v>57494</v>
@@ -708,7 +708,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -719,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pussen, Vg</t>
+          <t>Baskanäs, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338469</v>
+        <v>338430</v>
       </c>
       <c r="R2" t="n">
-        <v>6421084</v>
+        <v>6421185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524742</v>
+        <v>122524722</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -828,11 +832,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -843,14 +843,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baskanäs, Vg</t>
+          <t>Pussen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338430</v>
+        <v>338469</v>
       </c>
       <c r="R3" t="n">
-        <v>6421185</v>
+        <v>6421084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
